--- a/artfynd/A 42063-2024 artfynd.xlsx
+++ b/artfynd/A 42063-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120922516</v>
+        <v>120922581</v>
       </c>
       <c r="B5" t="n">
         <v>78598</v>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581511</v>
+        <v>581973</v>
       </c>
       <c r="R5" t="n">
-        <v>7194758</v>
+        <v>7193915</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120922581</v>
+        <v>120922516</v>
       </c>
       <c r="B6" t="n">
         <v>78598</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581973</v>
+        <v>581511</v>
       </c>
       <c r="R6" t="n">
-        <v>7193915</v>
+        <v>7194758</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2472,10 +2472,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120922540</v>
+        <v>120922568</v>
       </c>
       <c r="B18" t="n">
-        <v>78598</v>
+        <v>91127</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2484,25 +2484,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581580</v>
+        <v>581867</v>
       </c>
       <c r="R18" t="n">
-        <v>7194313</v>
+        <v>7194029</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2808,10 +2808,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120922568</v>
+        <v>120922540</v>
       </c>
       <c r="B21" t="n">
-        <v>91127</v>
+        <v>78598</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2820,25 +2820,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581867</v>
+        <v>581580</v>
       </c>
       <c r="R21" t="n">
-        <v>7194029</v>
+        <v>7194313</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2920,10 +2920,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120922497</v>
+        <v>120922517</v>
       </c>
       <c r="B22" t="n">
-        <v>57348</v>
+        <v>79715</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2932,43 +2932,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581664</v>
+        <v>581464</v>
       </c>
       <c r="R22" t="n">
-        <v>7194340</v>
+        <v>7194676</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3000,7 +2995,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,7 +3005,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3037,10 +3032,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120922517</v>
+        <v>120922490</v>
       </c>
       <c r="B23" t="n">
-        <v>79715</v>
+        <v>78598</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3049,25 +3044,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3077,10 +3072,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581464</v>
+        <v>581727</v>
       </c>
       <c r="R23" t="n">
-        <v>7194676</v>
+        <v>7194249</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3112,7 +3107,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3117,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3149,10 +3144,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120922490</v>
+        <v>120922531</v>
       </c>
       <c r="B24" t="n">
-        <v>78598</v>
+        <v>90652</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3161,25 +3156,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3189,10 +3184,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581727</v>
+        <v>581540</v>
       </c>
       <c r="R24" t="n">
-        <v>7194249</v>
+        <v>7194351</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3224,7 +3219,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3234,7 +3229,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3261,10 +3256,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120922531</v>
+        <v>120922491</v>
       </c>
       <c r="B25" t="n">
-        <v>90652</v>
+        <v>78598</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3273,25 +3268,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3301,10 +3296,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581540</v>
+        <v>581713</v>
       </c>
       <c r="R25" t="n">
-        <v>7194351</v>
+        <v>7194249</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3336,7 +3331,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3346,7 +3341,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3373,10 +3368,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120922491</v>
+        <v>120922497</v>
       </c>
       <c r="B26" t="n">
-        <v>78598</v>
+        <v>57348</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3389,34 +3384,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581713</v>
+        <v>581664</v>
       </c>
       <c r="R26" t="n">
-        <v>7194249</v>
+        <v>7194340</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -6518,10 +6518,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120922577</v>
+        <v>120922561</v>
       </c>
       <c r="B54" t="n">
-        <v>90687</v>
+        <v>90683</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6534,21 +6534,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6558,10 +6558,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581965</v>
+        <v>581708</v>
       </c>
       <c r="R54" t="n">
-        <v>7193917</v>
+        <v>7194148</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6630,10 +6630,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120922561</v>
+        <v>120922499</v>
       </c>
       <c r="B55" t="n">
-        <v>90683</v>
+        <v>78598</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6646,21 +6646,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6670,10 +6670,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581708</v>
+        <v>581705</v>
       </c>
       <c r="R55" t="n">
-        <v>7194148</v>
+        <v>7194365</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6705,7 +6705,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6742,10 +6742,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120922499</v>
+        <v>120922541</v>
       </c>
       <c r="B56" t="n">
-        <v>78598</v>
+        <v>74703</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6754,25 +6754,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6782,10 +6782,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581705</v>
+        <v>581586</v>
       </c>
       <c r="R56" t="n">
-        <v>7194365</v>
+        <v>7194270</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6817,7 +6817,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6854,10 +6854,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120922541</v>
+        <v>120922539</v>
       </c>
       <c r="B57" t="n">
-        <v>74703</v>
+        <v>79715</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6866,25 +6866,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6486</v>
+        <v>6464</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581586</v>
+        <v>581579</v>
       </c>
       <c r="R57" t="n">
-        <v>7194270</v>
+        <v>7194310</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6966,10 +6966,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120922539</v>
+        <v>120922577</v>
       </c>
       <c r="B58" t="n">
-        <v>79715</v>
+        <v>90687</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6978,25 +6978,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7006,10 +7006,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581579</v>
+        <v>581965</v>
       </c>
       <c r="R58" t="n">
-        <v>7194310</v>
+        <v>7193917</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7041,7 +7041,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7978,10 +7978,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120922535</v>
+        <v>120922518</v>
       </c>
       <c r="B67" t="n">
-        <v>79708</v>
+        <v>79680</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7990,25 +7990,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8018,10 +8018,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>581563</v>
+        <v>581464</v>
       </c>
       <c r="R67" t="n">
-        <v>7194343</v>
+        <v>7194676</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8053,7 +8053,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8090,10 +8090,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120922583</v>
+        <v>120922521</v>
       </c>
       <c r="B68" t="n">
-        <v>78598</v>
+        <v>79680</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8106,21 +8106,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8130,10 +8130,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>581974</v>
+        <v>581397</v>
       </c>
       <c r="R68" t="n">
-        <v>7193913</v>
+        <v>7194475</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8202,10 +8202,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120922518</v>
+        <v>120922535</v>
       </c>
       <c r="B69" t="n">
-        <v>79680</v>
+        <v>79708</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8214,25 +8214,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8242,10 +8242,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>581464</v>
+        <v>581563</v>
       </c>
       <c r="R69" t="n">
-        <v>7194676</v>
+        <v>7194343</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8314,10 +8314,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120922521</v>
+        <v>120922583</v>
       </c>
       <c r="B70" t="n">
-        <v>79680</v>
+        <v>78598</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8330,21 +8330,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8354,10 +8354,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>581397</v>
+        <v>581974</v>
       </c>
       <c r="R70" t="n">
-        <v>7194475</v>
+        <v>7193913</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8389,7 +8389,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 42063-2024 artfynd.xlsx
+++ b/artfynd/A 42063-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120922578</v>
+        <v>120922497</v>
       </c>
       <c r="B2" t="n">
-        <v>82382</v>
+        <v>57351</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581966</v>
+        <v>581664</v>
       </c>
       <c r="R2" t="n">
-        <v>7193919</v>
+        <v>7194340</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120922564</v>
+        <v>120922553</v>
       </c>
       <c r="B3" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581774</v>
+        <v>581589</v>
       </c>
       <c r="R3" t="n">
-        <v>7194115</v>
+        <v>7194225</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120922554</v>
+        <v>120922493</v>
       </c>
       <c r="B4" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581594</v>
+        <v>581641</v>
       </c>
       <c r="R4" t="n">
-        <v>7194228</v>
+        <v>7194292</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120922581</v>
+        <v>120922498</v>
       </c>
       <c r="B5" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581973</v>
+        <v>581663</v>
       </c>
       <c r="R5" t="n">
-        <v>7193915</v>
+        <v>7194338</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120922516</v>
+        <v>120922525</v>
       </c>
       <c r="B6" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581511</v>
+        <v>581482</v>
       </c>
       <c r="R6" t="n">
-        <v>7194758</v>
+        <v>7194429</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1198,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120922537</v>
+        <v>120922522</v>
       </c>
       <c r="B7" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581563</v>
+        <v>581402</v>
       </c>
       <c r="R7" t="n">
-        <v>7194343</v>
+        <v>7194474</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1310,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120922544</v>
+        <v>120922523</v>
       </c>
       <c r="B8" t="n">
-        <v>79715</v>
+        <v>79718</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581586</v>
+        <v>581415</v>
       </c>
       <c r="R8" t="n">
-        <v>7194249</v>
+        <v>7194476</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1422,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120922538</v>
+        <v>120922554</v>
       </c>
       <c r="B9" t="n">
-        <v>79714</v>
+        <v>78601</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1471,20 +1476,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1499,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581578</v>
+        <v>581594</v>
       </c>
       <c r="R9" t="n">
-        <v>7194309</v>
+        <v>7194228</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1534,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120922562</v>
+        <v>120922550</v>
       </c>
       <c r="B10" t="n">
-        <v>78598</v>
+        <v>79718</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1583,25 +1588,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581708</v>
+        <v>581585</v>
       </c>
       <c r="R10" t="n">
-        <v>7194148</v>
+        <v>7194233</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1646,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120922567</v>
+        <v>120922539</v>
       </c>
       <c r="B11" t="n">
-        <v>78598</v>
+        <v>79718</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1695,25 +1700,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581802</v>
+        <v>581579</v>
       </c>
       <c r="R11" t="n">
-        <v>7194113</v>
+        <v>7194310</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1758,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120922565</v>
+        <v>120922551</v>
       </c>
       <c r="B12" t="n">
-        <v>82382</v>
+        <v>79717</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1807,25 +1812,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>6463</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581743</v>
+        <v>581585</v>
       </c>
       <c r="R12" t="n">
-        <v>7194126</v>
+        <v>7194233</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1870,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120922570</v>
+        <v>120922558</v>
       </c>
       <c r="B13" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581870</v>
+        <v>581628</v>
       </c>
       <c r="R13" t="n">
-        <v>7194030</v>
+        <v>7194201</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1982,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120922530</v>
+        <v>120922582</v>
       </c>
       <c r="B14" t="n">
-        <v>78598</v>
+        <v>79718</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2031,25 +2036,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581521</v>
+        <v>581974</v>
       </c>
       <c r="R14" t="n">
-        <v>7194394</v>
+        <v>7193911</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2094,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2104,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120922545</v>
+        <v>120922491</v>
       </c>
       <c r="B15" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2171,7 +2176,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581586</v>
+        <v>581713</v>
       </c>
       <c r="R15" t="n">
         <v>7194249</v>
@@ -2206,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2216,7 +2221,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120922551</v>
+        <v>120922526</v>
       </c>
       <c r="B16" t="n">
-        <v>79714</v>
+        <v>90693</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,25 +2260,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>1108</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581585</v>
+        <v>581485</v>
       </c>
       <c r="R16" t="n">
-        <v>7194233</v>
+        <v>7194429</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2318,7 +2323,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2328,7 +2333,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,10 +2360,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120922495</v>
+        <v>120922569</v>
       </c>
       <c r="B17" t="n">
-        <v>57364</v>
+        <v>90697</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,39 +2376,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581553</v>
+        <v>581871</v>
       </c>
       <c r="R17" t="n">
-        <v>7194369</v>
+        <v>7194030</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,10 +2472,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120922568</v>
+        <v>120922524</v>
       </c>
       <c r="B18" t="n">
-        <v>91127</v>
+        <v>79682</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2484,25 +2484,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2512,10 +2512,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581867</v>
+        <v>581417</v>
       </c>
       <c r="R18" t="n">
-        <v>7194029</v>
+        <v>7194473</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2584,10 +2584,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120922523</v>
+        <v>120922552</v>
       </c>
       <c r="B19" t="n">
-        <v>79715</v>
+        <v>94496</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2600,21 +2600,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6464</v>
+        <v>2813</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581415</v>
+        <v>581589</v>
       </c>
       <c r="R19" t="n">
-        <v>7194476</v>
+        <v>7194225</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2659,7 +2659,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,7 +2669,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2696,10 +2696,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120922524</v>
+        <v>120922495</v>
       </c>
       <c r="B20" t="n">
-        <v>79679</v>
+        <v>57367</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2712,34 +2712,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581417</v>
+        <v>581553</v>
       </c>
       <c r="R20" t="n">
-        <v>7194473</v>
+        <v>7194369</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2771,7 +2776,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2781,7 +2786,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2808,10 +2813,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120922540</v>
+        <v>120922545</v>
       </c>
       <c r="B21" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2848,10 +2853,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581580</v>
+        <v>581586</v>
       </c>
       <c r="R21" t="n">
-        <v>7194313</v>
+        <v>7194249</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2883,7 +2888,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2893,7 +2898,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2920,10 +2925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120922517</v>
+        <v>120922574</v>
       </c>
       <c r="B22" t="n">
-        <v>79715</v>
+        <v>88024</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2932,25 +2937,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>510</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2960,10 +2965,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581464</v>
+        <v>581893</v>
       </c>
       <c r="R22" t="n">
-        <v>7194676</v>
+        <v>7193955</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2995,7 +3000,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3005,7 +3010,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3032,10 +3037,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120922490</v>
+        <v>120922555</v>
       </c>
       <c r="B23" t="n">
-        <v>78598</v>
+        <v>79648</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3044,25 +3049,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3072,10 +3077,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581727</v>
+        <v>581594</v>
       </c>
       <c r="R23" t="n">
-        <v>7194249</v>
+        <v>7194227</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3107,7 +3112,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3117,7 +3122,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3144,10 +3149,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120922531</v>
+        <v>120922547</v>
       </c>
       <c r="B24" t="n">
-        <v>90652</v>
+        <v>79683</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3156,25 +3161,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3184,10 +3189,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581540</v>
+        <v>581602</v>
       </c>
       <c r="R24" t="n">
-        <v>7194351</v>
+        <v>7194240</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3219,7 +3224,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3229,7 +3234,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3256,10 +3261,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120922491</v>
+        <v>120922549</v>
       </c>
       <c r="B25" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3296,10 +3301,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581713</v>
+        <v>581602</v>
       </c>
       <c r="R25" t="n">
-        <v>7194249</v>
+        <v>7194242</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3331,7 +3336,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3341,7 +3346,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3368,10 +3373,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120922497</v>
+        <v>120922562</v>
       </c>
       <c r="B26" t="n">
-        <v>57348</v>
+        <v>78601</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3384,39 +3389,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581664</v>
+        <v>581708</v>
       </c>
       <c r="R26" t="n">
-        <v>7194340</v>
+        <v>7194148</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3485,10 +3485,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120922559</v>
+        <v>120922494</v>
       </c>
       <c r="B27" t="n">
-        <v>97025</v>
+        <v>57504</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3497,38 +3497,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581685</v>
+        <v>581567</v>
       </c>
       <c r="R27" t="n">
-        <v>7194163</v>
+        <v>7194353</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3560,7 +3564,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3570,7 +3574,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3597,10 +3601,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120922546</v>
+        <v>120922577</v>
       </c>
       <c r="B28" t="n">
-        <v>94474</v>
+        <v>90697</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3609,25 +3613,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3637,10 +3641,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581593</v>
+        <v>581965</v>
       </c>
       <c r="R28" t="n">
-        <v>7194236</v>
+        <v>7193917</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3672,7 +3676,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3682,7 +3686,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3712,7 +3716,7 @@
         <v>120922527</v>
       </c>
       <c r="B29" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3821,10 +3825,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120922563</v>
+        <v>120922532</v>
       </c>
       <c r="B30" t="n">
-        <v>90683</v>
+        <v>57504</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3837,34 +3841,38 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1108</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581730</v>
+        <v>581557</v>
       </c>
       <c r="R30" t="n">
-        <v>7194140</v>
+        <v>7194351</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3896,7 +3904,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3906,7 +3914,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3933,10 +3941,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120922532</v>
+        <v>120922564</v>
       </c>
       <c r="B31" t="n">
-        <v>57501</v>
+        <v>78601</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3949,38 +3957,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581557</v>
+        <v>581774</v>
       </c>
       <c r="R31" t="n">
-        <v>7194351</v>
+        <v>7194115</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4012,7 +4016,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4022,7 +4026,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4049,10 +4053,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120922542</v>
+        <v>120922531</v>
       </c>
       <c r="B32" t="n">
-        <v>78598</v>
+        <v>90662</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4061,25 +4065,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4089,10 +4093,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581583</v>
+        <v>581540</v>
       </c>
       <c r="R32" t="n">
-        <v>7194274</v>
+        <v>7194351</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4124,7 +4128,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4134,7 +4138,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4161,10 +4165,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120922556</v>
+        <v>120922546</v>
       </c>
       <c r="B33" t="n">
-        <v>78687</v>
+        <v>94484</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4177,21 +4181,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6450</v>
+        <v>2809</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4204,7 +4208,7 @@
         <v>581593</v>
       </c>
       <c r="R33" t="n">
-        <v>7194223</v>
+        <v>7194236</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4236,7 +4240,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4246,7 +4250,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4273,10 +4277,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120922576</v>
+        <v>120922567</v>
       </c>
       <c r="B34" t="n">
-        <v>90973</v>
+        <v>78601</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4289,21 +4293,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4313,10 +4317,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581964</v>
+        <v>581802</v>
       </c>
       <c r="R34" t="n">
-        <v>7193918</v>
+        <v>7194113</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4348,7 +4352,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4358,7 +4362,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4385,10 +4389,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120922572</v>
+        <v>120922537</v>
       </c>
       <c r="B35" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4425,10 +4429,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581899</v>
+        <v>581563</v>
       </c>
       <c r="R35" t="n">
-        <v>7193983</v>
+        <v>7194343</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4460,7 +4464,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4470,7 +4474,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4497,10 +4501,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120922580</v>
+        <v>120922543</v>
       </c>
       <c r="B36" t="n">
-        <v>82382</v>
+        <v>79683</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4513,21 +4517,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4537,10 +4541,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581971</v>
+        <v>581586</v>
       </c>
       <c r="R36" t="n">
-        <v>7193909</v>
+        <v>7194249</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4572,7 +4576,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4582,7 +4586,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4609,10 +4613,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120922575</v>
+        <v>120922573</v>
       </c>
       <c r="B37" t="n">
-        <v>78598</v>
+        <v>90697</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4625,21 +4629,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4649,10 +4653,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581896</v>
+        <v>581899</v>
       </c>
       <c r="R37" t="n">
-        <v>7193954</v>
+        <v>7193981</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4684,7 +4688,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4694,7 +4698,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4721,10 +4725,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120922496</v>
+        <v>120922544</v>
       </c>
       <c r="B38" t="n">
-        <v>78598</v>
+        <v>79718</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4733,25 +4737,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4761,10 +4765,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581553</v>
+        <v>581586</v>
       </c>
       <c r="R38" t="n">
-        <v>7194365</v>
+        <v>7194249</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4796,7 +4800,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4806,7 +4810,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4833,10 +4837,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120922582</v>
+        <v>120922528</v>
       </c>
       <c r="B39" t="n">
-        <v>79715</v>
+        <v>78601</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4845,25 +4849,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4873,10 +4877,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581974</v>
+        <v>581492</v>
       </c>
       <c r="R39" t="n">
-        <v>7193911</v>
+        <v>7194428</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4908,7 +4912,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4918,7 +4922,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4945,10 +4949,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120922529</v>
+        <v>120922559</v>
       </c>
       <c r="B40" t="n">
-        <v>74705</v>
+        <v>97035</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4957,25 +4961,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4985,10 +4989,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>581524</v>
+        <v>581685</v>
       </c>
       <c r="R40" t="n">
-        <v>7194389</v>
+        <v>7194163</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5020,7 +5024,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5030,7 +5034,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5057,10 +5061,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120922520</v>
+        <v>120922561</v>
       </c>
       <c r="B41" t="n">
-        <v>57348</v>
+        <v>90693</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5073,39 +5077,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581375</v>
+        <v>581708</v>
       </c>
       <c r="R41" t="n">
-        <v>7194509</v>
+        <v>7194148</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5137,7 +5136,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5147,7 +5146,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5174,10 +5173,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120922547</v>
+        <v>120922520</v>
       </c>
       <c r="B42" t="n">
-        <v>79680</v>
+        <v>57351</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5190,34 +5189,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581602</v>
+        <v>581375</v>
       </c>
       <c r="R42" t="n">
-        <v>7194240</v>
+        <v>7194509</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5249,7 +5253,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5259,7 +5263,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5286,10 +5290,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120922552</v>
+        <v>120922518</v>
       </c>
       <c r="B43" t="n">
-        <v>94486</v>
+        <v>79683</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5298,25 +5302,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2813</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5326,10 +5330,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581589</v>
+        <v>581464</v>
       </c>
       <c r="R43" t="n">
-        <v>7194225</v>
+        <v>7194676</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5361,7 +5365,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5371,7 +5375,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5398,10 +5402,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120922519</v>
+        <v>120922576</v>
       </c>
       <c r="B44" t="n">
-        <v>79680</v>
+        <v>90983</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5414,21 +5418,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2081</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5438,10 +5442,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581392</v>
+        <v>581964</v>
       </c>
       <c r="R44" t="n">
-        <v>7194541</v>
+        <v>7193918</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5473,7 +5477,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5483,7 +5487,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5510,10 +5514,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120922571</v>
+        <v>120922538</v>
       </c>
       <c r="B45" t="n">
-        <v>78598</v>
+        <v>79717</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5522,20 +5526,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5550,10 +5554,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581891</v>
+        <v>581578</v>
       </c>
       <c r="R45" t="n">
-        <v>7193993</v>
+        <v>7194309</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5585,7 +5589,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5595,7 +5599,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5622,10 +5626,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120922549</v>
+        <v>120922540</v>
       </c>
       <c r="B46" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5662,10 +5666,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581602</v>
+        <v>581580</v>
       </c>
       <c r="R46" t="n">
-        <v>7194242</v>
+        <v>7194313</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5697,7 +5701,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5707,7 +5711,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5734,10 +5738,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120922526</v>
+        <v>120922578</v>
       </c>
       <c r="B47" t="n">
-        <v>90683</v>
+        <v>82385</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5750,21 +5754,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5774,10 +5778,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581485</v>
+        <v>581966</v>
       </c>
       <c r="R47" t="n">
-        <v>7194429</v>
+        <v>7193919</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5809,7 +5813,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5819,7 +5823,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5846,10 +5850,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120922558</v>
+        <v>120922541</v>
       </c>
       <c r="B48" t="n">
-        <v>78598</v>
+        <v>74706</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5858,25 +5862,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5886,10 +5890,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581628</v>
+        <v>581586</v>
       </c>
       <c r="R48" t="n">
-        <v>7194201</v>
+        <v>7194270</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5921,7 +5925,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5931,7 +5935,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5958,10 +5962,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120922528</v>
+        <v>120922579</v>
       </c>
       <c r="B49" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5998,10 +6002,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581492</v>
+        <v>581970</v>
       </c>
       <c r="R49" t="n">
-        <v>7194428</v>
+        <v>7193921</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6033,7 +6037,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6043,7 +6047,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6070,10 +6074,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120922492</v>
+        <v>120922517</v>
       </c>
       <c r="B50" t="n">
-        <v>91042</v>
+        <v>79718</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6082,25 +6086,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1506</v>
+        <v>6464</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6110,10 +6114,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581638</v>
+        <v>581464</v>
       </c>
       <c r="R50" t="n">
-        <v>7194287</v>
+        <v>7194676</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6145,7 +6149,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6155,7 +6159,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6182,10 +6186,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120922493</v>
+        <v>120922570</v>
       </c>
       <c r="B51" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6222,10 +6226,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581641</v>
+        <v>581870</v>
       </c>
       <c r="R51" t="n">
-        <v>7194292</v>
+        <v>7194030</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6257,7 +6261,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6267,7 +6271,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6294,10 +6298,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120922550</v>
+        <v>120922560</v>
       </c>
       <c r="B52" t="n">
-        <v>79715</v>
+        <v>78601</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6306,25 +6310,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6334,10 +6338,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581585</v>
+        <v>581688</v>
       </c>
       <c r="R52" t="n">
-        <v>7194233</v>
+        <v>7194164</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6369,7 +6373,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6379,7 +6383,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6406,10 +6410,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120922548</v>
+        <v>120922535</v>
       </c>
       <c r="B53" t="n">
-        <v>79715</v>
+        <v>79711</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6422,21 +6426,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6446,10 +6450,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581602</v>
+        <v>581563</v>
       </c>
       <c r="R53" t="n">
-        <v>7194242</v>
+        <v>7194343</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6481,7 +6485,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6491,7 +6495,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6518,10 +6522,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120922561</v>
+        <v>120922575</v>
       </c>
       <c r="B54" t="n">
-        <v>90683</v>
+        <v>78601</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6534,21 +6538,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6558,10 +6562,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581708</v>
+        <v>581896</v>
       </c>
       <c r="R54" t="n">
-        <v>7194148</v>
+        <v>7193954</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6593,7 +6597,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6603,7 +6607,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6630,10 +6634,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120922499</v>
+        <v>120922572</v>
       </c>
       <c r="B55" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6670,10 +6674,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581705</v>
+        <v>581899</v>
       </c>
       <c r="R55" t="n">
-        <v>7194365</v>
+        <v>7193983</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6705,7 +6709,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6715,7 +6719,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6742,10 +6746,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120922541</v>
+        <v>120922534</v>
       </c>
       <c r="B56" t="n">
-        <v>74703</v>
+        <v>79683</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6754,25 +6758,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6486</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6782,10 +6786,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581586</v>
+        <v>581561</v>
       </c>
       <c r="R56" t="n">
-        <v>7194270</v>
+        <v>7194344</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6817,7 +6821,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6827,7 +6831,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6854,10 +6858,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120922539</v>
+        <v>120922530</v>
       </c>
       <c r="B57" t="n">
-        <v>79715</v>
+        <v>78601</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6866,25 +6870,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6894,10 +6898,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581579</v>
+        <v>581521</v>
       </c>
       <c r="R57" t="n">
-        <v>7194310</v>
+        <v>7194394</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6929,7 +6933,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6939,7 +6943,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6966,10 +6970,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120922577</v>
+        <v>120922565</v>
       </c>
       <c r="B58" t="n">
-        <v>90687</v>
+        <v>82385</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6982,21 +6986,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7006,10 +7010,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581965</v>
+        <v>581743</v>
       </c>
       <c r="R58" t="n">
-        <v>7193917</v>
+        <v>7194126</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7041,7 +7045,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7051,7 +7055,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7078,10 +7082,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120922543</v>
+        <v>120922492</v>
       </c>
       <c r="B59" t="n">
-        <v>79680</v>
+        <v>91052</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7090,25 +7094,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2081</v>
+        <v>1506</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7118,10 +7122,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581586</v>
+        <v>581638</v>
       </c>
       <c r="R59" t="n">
-        <v>7194249</v>
+        <v>7194287</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7153,7 +7157,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7163,7 +7167,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7190,10 +7194,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120922534</v>
+        <v>120922519</v>
       </c>
       <c r="B60" t="n">
-        <v>79680</v>
+        <v>79683</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7230,10 +7234,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581561</v>
+        <v>581392</v>
       </c>
       <c r="R60" t="n">
-        <v>7194344</v>
+        <v>7194541</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7265,7 +7269,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7275,7 +7279,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7302,10 +7306,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120922522</v>
+        <v>120922566</v>
       </c>
       <c r="B61" t="n">
-        <v>79679</v>
+        <v>78601</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7318,21 +7322,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7342,10 +7346,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581402</v>
+        <v>581743</v>
       </c>
       <c r="R61" t="n">
-        <v>7194474</v>
+        <v>7194127</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7377,7 +7381,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7387,7 +7391,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7414,10 +7418,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120922494</v>
+        <v>120922557</v>
       </c>
       <c r="B62" t="n">
-        <v>57501</v>
+        <v>97035</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7426,42 +7430,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581567</v>
+        <v>581627</v>
       </c>
       <c r="R62" t="n">
-        <v>7194353</v>
+        <v>7194202</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7493,7 +7493,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7530,10 +7530,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120922574</v>
+        <v>120922571</v>
       </c>
       <c r="B63" t="n">
-        <v>88018</v>
+        <v>78601</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7546,21 +7546,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7570,10 +7570,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>581893</v>
+        <v>581891</v>
       </c>
       <c r="R63" t="n">
-        <v>7193955</v>
+        <v>7193993</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7605,7 +7605,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7642,10 +7642,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120922569</v>
+        <v>120922521</v>
       </c>
       <c r="B64" t="n">
-        <v>90687</v>
+        <v>79683</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7658,21 +7658,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7682,10 +7682,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>581871</v>
+        <v>581397</v>
       </c>
       <c r="R64" t="n">
-        <v>7194030</v>
+        <v>7194475</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7754,10 +7754,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120922553</v>
+        <v>120922563</v>
       </c>
       <c r="B65" t="n">
-        <v>78598</v>
+        <v>90693</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7770,21 +7770,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7794,10 +7794,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>581589</v>
+        <v>581730</v>
       </c>
       <c r="R65" t="n">
-        <v>7194225</v>
+        <v>7194140</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7866,10 +7866,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120922533</v>
+        <v>120922548</v>
       </c>
       <c r="B66" t="n">
-        <v>79679</v>
+        <v>79718</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7878,25 +7878,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7906,10 +7906,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>581561</v>
+        <v>581602</v>
       </c>
       <c r="R66" t="n">
-        <v>7194344</v>
+        <v>7194242</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7941,7 +7941,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7978,10 +7978,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120922518</v>
+        <v>120922516</v>
       </c>
       <c r="B67" t="n">
-        <v>79680</v>
+        <v>78601</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7994,21 +7994,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8018,10 +8018,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>581464</v>
+        <v>581511</v>
       </c>
       <c r="R67" t="n">
-        <v>7194676</v>
+        <v>7194758</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8053,7 +8053,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8090,10 +8090,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120922521</v>
+        <v>120922581</v>
       </c>
       <c r="B68" t="n">
-        <v>79680</v>
+        <v>78601</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8106,21 +8106,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8130,10 +8130,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>581397</v>
+        <v>581973</v>
       </c>
       <c r="R68" t="n">
-        <v>7194475</v>
+        <v>7193915</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8202,10 +8202,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120922535</v>
+        <v>120922580</v>
       </c>
       <c r="B69" t="n">
-        <v>79708</v>
+        <v>82385</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8214,25 +8214,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8242,10 +8242,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>581563</v>
+        <v>581971</v>
       </c>
       <c r="R69" t="n">
-        <v>7194343</v>
+        <v>7193909</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8314,10 +8314,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120922583</v>
+        <v>120922490</v>
       </c>
       <c r="B70" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8354,10 +8354,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>581974</v>
+        <v>581727</v>
       </c>
       <c r="R70" t="n">
-        <v>7193913</v>
+        <v>7194249</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8389,7 +8389,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8426,10 +8426,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120922498</v>
+        <v>120922542</v>
       </c>
       <c r="B71" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8466,10 +8466,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>581663</v>
+        <v>581583</v>
       </c>
       <c r="R71" t="n">
-        <v>7194338</v>
+        <v>7194274</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8538,10 +8538,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120922566</v>
+        <v>120922583</v>
       </c>
       <c r="B72" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8578,10 +8578,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>581743</v>
+        <v>581974</v>
       </c>
       <c r="R72" t="n">
-        <v>7194127</v>
+        <v>7193913</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8613,7 +8613,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8650,10 +8650,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120922573</v>
+        <v>120922536</v>
       </c>
       <c r="B73" t="n">
-        <v>90687</v>
+        <v>79718</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8662,25 +8662,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8690,10 +8690,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>581899</v>
+        <v>581563</v>
       </c>
       <c r="R73" t="n">
-        <v>7193981</v>
+        <v>7194343</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8762,10 +8762,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120922560</v>
+        <v>120922533</v>
       </c>
       <c r="B74" t="n">
-        <v>78598</v>
+        <v>79682</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8778,21 +8778,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8802,10 +8802,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>581688</v>
+        <v>581561</v>
       </c>
       <c r="R74" t="n">
-        <v>7194164</v>
+        <v>7194344</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8837,7 +8837,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8874,10 +8874,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120922536</v>
+        <v>120922499</v>
       </c>
       <c r="B75" t="n">
-        <v>79715</v>
+        <v>78601</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8886,25 +8886,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8914,10 +8914,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>581563</v>
+        <v>581705</v>
       </c>
       <c r="R75" t="n">
-        <v>7194343</v>
+        <v>7194365</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8949,7 +8949,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8986,10 +8986,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120922579</v>
+        <v>120922568</v>
       </c>
       <c r="B76" t="n">
-        <v>78598</v>
+        <v>91137</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8998,25 +8998,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9026,10 +9026,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>581970</v>
+        <v>581867</v>
       </c>
       <c r="R76" t="n">
-        <v>7193921</v>
+        <v>7194029</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9061,7 +9061,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9098,10 +9098,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120922525</v>
+        <v>120922496</v>
       </c>
       <c r="B77" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9138,10 +9138,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>581482</v>
+        <v>581553</v>
       </c>
       <c r="R77" t="n">
-        <v>7194429</v>
+        <v>7194365</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9173,7 +9173,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9210,10 +9210,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120922557</v>
+        <v>120922556</v>
       </c>
       <c r="B78" t="n">
-        <v>97025</v>
+        <v>78690</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9226,21 +9226,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221945</v>
+        <v>6450</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>581627</v>
+        <v>581593</v>
       </c>
       <c r="R78" t="n">
-        <v>7194202</v>
+        <v>7194223</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9285,7 +9285,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9322,10 +9322,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120922555</v>
+        <v>120922529</v>
       </c>
       <c r="B79" t="n">
-        <v>79645</v>
+        <v>74708</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9334,25 +9334,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229748</v>
+        <v>6440</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9362,10 +9362,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>581594</v>
+        <v>581524</v>
       </c>
       <c r="R79" t="n">
-        <v>7194227</v>
+        <v>7194389</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD79" t="b">

--- a/artfynd/A 42063-2024 artfynd.xlsx
+++ b/artfynd/A 42063-2024 artfynd.xlsx
@@ -7418,10 +7418,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120922557</v>
+        <v>120922571</v>
       </c>
       <c r="B62" t="n">
-        <v>97035</v>
+        <v>78601</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7430,25 +7430,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7458,10 +7458,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581627</v>
+        <v>581891</v>
       </c>
       <c r="R62" t="n">
-        <v>7194202</v>
+        <v>7193993</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7493,7 +7493,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7530,10 +7530,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120922571</v>
+        <v>120922521</v>
       </c>
       <c r="B63" t="n">
-        <v>78601</v>
+        <v>79683</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7546,21 +7546,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7570,10 +7570,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>581891</v>
+        <v>581397</v>
       </c>
       <c r="R63" t="n">
-        <v>7193993</v>
+        <v>7194475</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7605,7 +7605,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7642,10 +7642,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120922521</v>
+        <v>120922557</v>
       </c>
       <c r="B64" t="n">
-        <v>79683</v>
+        <v>97035</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7654,25 +7654,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2081</v>
+        <v>221945</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7682,10 +7682,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>581397</v>
+        <v>581627</v>
       </c>
       <c r="R64" t="n">
-        <v>7194475</v>
+        <v>7194202</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD64" t="b">

--- a/artfynd/A 42063-2024 artfynd.xlsx
+++ b/artfynd/A 42063-2024 artfynd.xlsx
@@ -1800,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120922551</v>
+        <v>120922526</v>
       </c>
       <c r="B12" t="n">
-        <v>79717</v>
+        <v>90693</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1812,25 +1812,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581585</v>
+        <v>581485</v>
       </c>
       <c r="R12" t="n">
-        <v>7194233</v>
+        <v>7194429</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120922558</v>
+        <v>120922551</v>
       </c>
       <c r="B13" t="n">
-        <v>78601</v>
+        <v>79717</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1924,20 +1924,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1952,10 +1952,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581628</v>
+        <v>581585</v>
       </c>
       <c r="R13" t="n">
-        <v>7194201</v>
+        <v>7194233</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,10 +2024,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120922582</v>
+        <v>120922558</v>
       </c>
       <c r="B14" t="n">
-        <v>79718</v>
+        <v>78601</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,25 +2036,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581974</v>
+        <v>581628</v>
       </c>
       <c r="R14" t="n">
-        <v>7193911</v>
+        <v>7194201</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,10 +2136,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120922491</v>
+        <v>120922582</v>
       </c>
       <c r="B15" t="n">
-        <v>78601</v>
+        <v>79718</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2148,25 +2148,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2176,10 +2176,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581713</v>
+        <v>581974</v>
       </c>
       <c r="R15" t="n">
-        <v>7194249</v>
+        <v>7193911</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2248,10 +2248,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120922526</v>
+        <v>120922491</v>
       </c>
       <c r="B16" t="n">
-        <v>90693</v>
+        <v>78601</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,21 +2264,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581485</v>
+        <v>581713</v>
       </c>
       <c r="R16" t="n">
-        <v>7194429</v>
+        <v>7194249</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2925,10 +2925,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120922574</v>
+        <v>120922494</v>
       </c>
       <c r="B22" t="n">
-        <v>88024</v>
+        <v>57504</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2941,34 +2941,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>510</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581893</v>
+        <v>581567</v>
       </c>
       <c r="R22" t="n">
-        <v>7193955</v>
+        <v>7194353</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3000,7 +3004,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3010,7 +3014,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3037,10 +3041,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120922555</v>
+        <v>120922574</v>
       </c>
       <c r="B23" t="n">
-        <v>79648</v>
+        <v>88024</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3049,25 +3053,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229748</v>
+        <v>510</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3077,10 +3081,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581594</v>
+        <v>581893</v>
       </c>
       <c r="R23" t="n">
-        <v>7194227</v>
+        <v>7193955</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3112,7 +3116,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3122,7 +3126,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3485,10 +3489,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120922494</v>
+        <v>120922555</v>
       </c>
       <c r="B27" t="n">
-        <v>57504</v>
+        <v>79648</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3497,42 +3501,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>229748</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581567</v>
+        <v>581594</v>
       </c>
       <c r="R27" t="n">
-        <v>7194353</v>
+        <v>7194227</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -7418,10 +7418,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120922571</v>
+        <v>120922557</v>
       </c>
       <c r="B62" t="n">
-        <v>78601</v>
+        <v>97035</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7430,25 +7430,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7458,10 +7458,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581891</v>
+        <v>581627</v>
       </c>
       <c r="R62" t="n">
-        <v>7193993</v>
+        <v>7194202</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7493,7 +7493,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7530,10 +7530,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120922521</v>
+        <v>120922571</v>
       </c>
       <c r="B63" t="n">
-        <v>79683</v>
+        <v>78601</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7546,21 +7546,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7570,10 +7570,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>581397</v>
+        <v>581891</v>
       </c>
       <c r="R63" t="n">
-        <v>7194475</v>
+        <v>7193993</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7605,7 +7605,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7642,10 +7642,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120922557</v>
+        <v>120922521</v>
       </c>
       <c r="B64" t="n">
-        <v>97035</v>
+        <v>79683</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7654,25 +7654,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221945</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7682,10 +7682,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>581627</v>
+        <v>581397</v>
       </c>
       <c r="R64" t="n">
-        <v>7194202</v>
+        <v>7194475</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD64" t="b">

--- a/artfynd/A 42063-2024 artfynd.xlsx
+++ b/artfynd/A 42063-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120922497</v>
+        <v>120922527</v>
       </c>
       <c r="B2" t="n">
-        <v>57351</v>
+        <v>90697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581664</v>
+        <v>581494</v>
       </c>
       <c r="R2" t="n">
-        <v>7194340</v>
+        <v>7194437</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120922553</v>
+        <v>120922572</v>
       </c>
       <c r="B3" t="n">
         <v>78601</v>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581589</v>
+        <v>581899</v>
       </c>
       <c r="R3" t="n">
-        <v>7194225</v>
+        <v>7193983</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120922493</v>
+        <v>120922579</v>
       </c>
       <c r="B4" t="n">
         <v>78601</v>
@@ -944,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581641</v>
+        <v>581970</v>
       </c>
       <c r="R4" t="n">
-        <v>7194292</v>
+        <v>7193921</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120922498</v>
+        <v>120922549</v>
       </c>
       <c r="B5" t="n">
         <v>78601</v>
@@ -1056,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581663</v>
+        <v>581602</v>
       </c>
       <c r="R5" t="n">
-        <v>7194338</v>
+        <v>7194242</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120922525</v>
+        <v>120922522</v>
       </c>
       <c r="B6" t="n">
-        <v>78601</v>
+        <v>79682</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581482</v>
+        <v>581402</v>
       </c>
       <c r="R6" t="n">
-        <v>7194429</v>
+        <v>7194474</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120922522</v>
+        <v>120922532</v>
       </c>
       <c r="B7" t="n">
-        <v>79682</v>
+        <v>57504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,34 +1251,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581402</v>
+        <v>581557</v>
       </c>
       <c r="R7" t="n">
-        <v>7194474</v>
+        <v>7194351</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1314,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1324,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1351,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120922523</v>
+        <v>120922547</v>
       </c>
       <c r="B8" t="n">
-        <v>79718</v>
+        <v>79683</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1364,25 +1363,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581415</v>
+        <v>581602</v>
       </c>
       <c r="R8" t="n">
-        <v>7194476</v>
+        <v>7194240</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1463,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120922554</v>
+        <v>120922535</v>
       </c>
       <c r="B9" t="n">
-        <v>78601</v>
+        <v>79711</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,25 +1475,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1503,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581594</v>
+        <v>581563</v>
       </c>
       <c r="R9" t="n">
-        <v>7194228</v>
+        <v>7194343</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1539,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120922550</v>
+        <v>120922525</v>
       </c>
       <c r="B10" t="n">
-        <v>79718</v>
+        <v>78601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1588,25 +1587,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581585</v>
+        <v>581482</v>
       </c>
       <c r="R10" t="n">
-        <v>7194233</v>
+        <v>7194429</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1651,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,10 +1687,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120922539</v>
+        <v>120922528</v>
       </c>
       <c r="B11" t="n">
-        <v>79718</v>
+        <v>78601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1700,25 +1699,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1728,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581579</v>
+        <v>581492</v>
       </c>
       <c r="R11" t="n">
-        <v>7194310</v>
+        <v>7194428</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1763,7 +1762,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1772,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,10 +1799,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120922526</v>
+        <v>120922543</v>
       </c>
       <c r="B12" t="n">
-        <v>90693</v>
+        <v>79683</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,21 +1815,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1839,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581485</v>
+        <v>581586</v>
       </c>
       <c r="R12" t="n">
-        <v>7194429</v>
+        <v>7194249</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1875,7 +1874,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1884,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1911,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120922551</v>
+        <v>120922561</v>
       </c>
       <c r="B13" t="n">
-        <v>79717</v>
+        <v>90693</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1924,25 +1923,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6463</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1952,10 +1951,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581585</v>
+        <v>581708</v>
       </c>
       <c r="R13" t="n">
-        <v>7194233</v>
+        <v>7194148</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1987,7 +1986,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1997,7 +1996,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,10 +2023,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120922558</v>
+        <v>120922578</v>
       </c>
       <c r="B14" t="n">
-        <v>78601</v>
+        <v>82385</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2040,21 +2039,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2064,10 +2063,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581628</v>
+        <v>581966</v>
       </c>
       <c r="R14" t="n">
-        <v>7194201</v>
+        <v>7193919</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2099,7 +2098,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2109,7 +2108,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,10 +2135,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120922582</v>
+        <v>120922583</v>
       </c>
       <c r="B15" t="n">
-        <v>79718</v>
+        <v>78601</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2148,25 +2147,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2179,7 +2178,7 @@
         <v>581974</v>
       </c>
       <c r="R15" t="n">
-        <v>7193911</v>
+        <v>7193913</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2248,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120922491</v>
+        <v>120922565</v>
       </c>
       <c r="B16" t="n">
-        <v>78601</v>
+        <v>82385</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2264,21 +2263,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2288,10 +2287,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581713</v>
+        <v>581743</v>
       </c>
       <c r="R16" t="n">
-        <v>7194249</v>
+        <v>7194126</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2323,7 +2322,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2333,7 +2332,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,10 +2359,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120922569</v>
+        <v>120922576</v>
       </c>
       <c r="B17" t="n">
-        <v>90697</v>
+        <v>90983</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2376,21 +2375,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2400,10 +2399,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581871</v>
+        <v>581964</v>
       </c>
       <c r="R17" t="n">
-        <v>7194030</v>
+        <v>7193918</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2435,7 +2434,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2445,7 +2444,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,10 +2471,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120922524</v>
+        <v>120922492</v>
       </c>
       <c r="B18" t="n">
-        <v>79682</v>
+        <v>91052</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2484,25 +2483,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1506</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2512,10 +2511,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581417</v>
+        <v>581638</v>
       </c>
       <c r="R18" t="n">
-        <v>7194473</v>
+        <v>7194287</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2547,7 +2546,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2557,7 +2556,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2584,10 +2583,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120922552</v>
+        <v>120922563</v>
       </c>
       <c r="B19" t="n">
-        <v>94496</v>
+        <v>90693</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2596,25 +2595,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2813</v>
+        <v>1108</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogshakmossa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus subpinnatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lindb.) T.J.Kop.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2624,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581589</v>
+        <v>581730</v>
       </c>
       <c r="R19" t="n">
-        <v>7194225</v>
+        <v>7194140</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2659,7 +2658,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2669,7 +2668,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:54</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2696,10 +2695,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120922495</v>
+        <v>120922490</v>
       </c>
       <c r="B20" t="n">
-        <v>57367</v>
+        <v>78601</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2712,39 +2711,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581553</v>
+        <v>581727</v>
       </c>
       <c r="R20" t="n">
-        <v>7194369</v>
+        <v>7194249</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2776,7 +2770,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2786,7 +2780,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2813,10 +2807,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120922545</v>
+        <v>120922536</v>
       </c>
       <c r="B21" t="n">
-        <v>78601</v>
+        <v>79718</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2825,25 +2819,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2853,10 +2847,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581586</v>
+        <v>581563</v>
       </c>
       <c r="R21" t="n">
-        <v>7194249</v>
+        <v>7194343</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2888,7 +2882,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2898,7 +2892,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2925,10 +2919,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120922494</v>
+        <v>120922546</v>
       </c>
       <c r="B22" t="n">
-        <v>57504</v>
+        <v>94484</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2937,42 +2931,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>2809</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>581567</v>
+        <v>581593</v>
       </c>
       <c r="R22" t="n">
-        <v>7194353</v>
+        <v>7194236</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3004,7 +2994,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3014,7 +3004,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3041,10 +3031,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120922574</v>
+        <v>120922570</v>
       </c>
       <c r="B23" t="n">
-        <v>88024</v>
+        <v>78601</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3057,21 +3047,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3081,10 +3071,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581893</v>
+        <v>581870</v>
       </c>
       <c r="R23" t="n">
-        <v>7193955</v>
+        <v>7194030</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3116,7 +3106,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3126,7 +3116,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3153,10 +3143,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120922547</v>
+        <v>120922553</v>
       </c>
       <c r="B24" t="n">
-        <v>79683</v>
+        <v>78601</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3169,21 +3159,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3193,10 +3183,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581602</v>
+        <v>581589</v>
       </c>
       <c r="R24" t="n">
-        <v>7194240</v>
+        <v>7194225</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3228,7 +3218,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3238,7 +3228,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3265,7 +3255,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120922549</v>
+        <v>120922545</v>
       </c>
       <c r="B25" t="n">
         <v>78601</v>
@@ -3305,10 +3295,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>581602</v>
+        <v>581586</v>
       </c>
       <c r="R25" t="n">
-        <v>7194242</v>
+        <v>7194249</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3340,7 +3330,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3350,7 +3340,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3377,10 +3367,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120922562</v>
+        <v>120922582</v>
       </c>
       <c r="B26" t="n">
-        <v>78601</v>
+        <v>79718</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3389,25 +3379,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3417,10 +3407,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>581708</v>
+        <v>581974</v>
       </c>
       <c r="R26" t="n">
-        <v>7194148</v>
+        <v>7193911</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3452,7 +3442,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3462,7 +3452,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3489,10 +3479,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120922555</v>
+        <v>120922554</v>
       </c>
       <c r="B27" t="n">
-        <v>79648</v>
+        <v>78601</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3501,25 +3491,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3532,7 +3522,7 @@
         <v>581594</v>
       </c>
       <c r="R27" t="n">
-        <v>7194227</v>
+        <v>7194228</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3564,7 +3554,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3574,7 +3564,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3601,10 +3591,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120922577</v>
+        <v>120922540</v>
       </c>
       <c r="B28" t="n">
-        <v>90697</v>
+        <v>78601</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3617,21 +3607,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3641,10 +3631,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581965</v>
+        <v>581580</v>
       </c>
       <c r="R28" t="n">
-        <v>7193917</v>
+        <v>7194313</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3676,7 +3666,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3686,7 +3676,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3713,10 +3703,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120922527</v>
+        <v>120922537</v>
       </c>
       <c r="B29" t="n">
-        <v>90697</v>
+        <v>78601</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3729,21 +3719,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3753,10 +3743,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>581494</v>
+        <v>581563</v>
       </c>
       <c r="R29" t="n">
-        <v>7194437</v>
+        <v>7194343</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3788,7 +3778,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3798,7 +3788,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3825,10 +3815,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120922532</v>
+        <v>120922555</v>
       </c>
       <c r="B30" t="n">
-        <v>57504</v>
+        <v>79648</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3837,42 +3827,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>229748</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>581557</v>
+        <v>581594</v>
       </c>
       <c r="R30" t="n">
-        <v>7194351</v>
+        <v>7194227</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3904,7 +3890,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3914,7 +3900,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3941,7 +3927,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120922564</v>
+        <v>120922571</v>
       </c>
       <c r="B31" t="n">
         <v>78601</v>
@@ -3981,10 +3967,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>581774</v>
+        <v>581891</v>
       </c>
       <c r="R31" t="n">
-        <v>7194115</v>
+        <v>7193993</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4016,7 +4002,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4026,7 +4012,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4053,10 +4039,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120922531</v>
+        <v>120922499</v>
       </c>
       <c r="B32" t="n">
-        <v>90662</v>
+        <v>78601</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4065,25 +4051,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4093,10 +4079,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>581540</v>
+        <v>581705</v>
       </c>
       <c r="R32" t="n">
-        <v>7194351</v>
+        <v>7194365</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4128,7 +4114,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4138,7 +4124,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4165,10 +4151,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120922546</v>
+        <v>120922551</v>
       </c>
       <c r="B33" t="n">
-        <v>94484</v>
+        <v>79717</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4181,21 +4167,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2809</v>
+        <v>6463</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4205,10 +4191,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>581593</v>
+        <v>581585</v>
       </c>
       <c r="R33" t="n">
-        <v>7194236</v>
+        <v>7194233</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4240,7 +4226,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4250,7 +4236,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4277,7 +4263,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120922567</v>
+        <v>120922560</v>
       </c>
       <c r="B34" t="n">
         <v>78601</v>
@@ -4317,10 +4303,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>581802</v>
+        <v>581688</v>
       </c>
       <c r="R34" t="n">
-        <v>7194113</v>
+        <v>7194164</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4352,7 +4338,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4362,7 +4348,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4389,10 +4375,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120922537</v>
+        <v>120922548</v>
       </c>
       <c r="B35" t="n">
-        <v>78601</v>
+        <v>79718</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4401,25 +4387,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4429,10 +4415,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>581563</v>
+        <v>581602</v>
       </c>
       <c r="R35" t="n">
-        <v>7194343</v>
+        <v>7194242</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4464,7 +4450,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4474,7 +4460,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4501,10 +4487,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120922543</v>
+        <v>120922516</v>
       </c>
       <c r="B36" t="n">
-        <v>79683</v>
+        <v>78601</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4517,21 +4503,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4541,10 +4527,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>581586</v>
+        <v>581511</v>
       </c>
       <c r="R36" t="n">
-        <v>7194249</v>
+        <v>7194758</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4576,7 +4562,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4586,7 +4572,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4613,10 +4599,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120922573</v>
+        <v>120922558</v>
       </c>
       <c r="B37" t="n">
-        <v>90697</v>
+        <v>78601</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4629,21 +4615,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4653,10 +4639,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>581899</v>
+        <v>581628</v>
       </c>
       <c r="R37" t="n">
-        <v>7193981</v>
+        <v>7194201</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4688,7 +4674,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4698,7 +4684,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4725,10 +4711,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120922544</v>
+        <v>120922520</v>
       </c>
       <c r="B38" t="n">
-        <v>79718</v>
+        <v>57351</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4737,38 +4723,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>581586</v>
+        <v>581375</v>
       </c>
       <c r="R38" t="n">
-        <v>7194249</v>
+        <v>7194509</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4800,7 +4791,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4810,7 +4801,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4837,10 +4828,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120922528</v>
+        <v>120922497</v>
       </c>
       <c r="B39" t="n">
-        <v>78601</v>
+        <v>57351</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4853,34 +4844,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>581492</v>
+        <v>581664</v>
       </c>
       <c r="R39" t="n">
-        <v>7194428</v>
+        <v>7194340</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4912,7 +4908,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4922,7 +4918,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5061,10 +5057,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120922561</v>
+        <v>120922574</v>
       </c>
       <c r="B41" t="n">
-        <v>90693</v>
+        <v>88024</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5077,21 +5073,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1108</v>
+        <v>510</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5101,10 +5097,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>581708</v>
+        <v>581893</v>
       </c>
       <c r="R41" t="n">
-        <v>7194148</v>
+        <v>7193955</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5136,7 +5132,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5146,7 +5142,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5173,10 +5169,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120922520</v>
+        <v>120922521</v>
       </c>
       <c r="B42" t="n">
-        <v>57351</v>
+        <v>79683</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5189,39 +5185,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>581375</v>
+        <v>581397</v>
       </c>
       <c r="R42" t="n">
-        <v>7194509</v>
+        <v>7194475</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5253,7 +5244,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5263,7 +5254,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5290,10 +5281,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120922518</v>
+        <v>120922524</v>
       </c>
       <c r="B43" t="n">
-        <v>79683</v>
+        <v>79682</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5306,21 +5297,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5330,10 +5321,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>581464</v>
+        <v>581417</v>
       </c>
       <c r="R43" t="n">
-        <v>7194676</v>
+        <v>7194473</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5365,7 +5356,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5375,7 +5366,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5402,10 +5393,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120922576</v>
+        <v>120922530</v>
       </c>
       <c r="B44" t="n">
-        <v>90983</v>
+        <v>78601</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5418,21 +5409,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5442,10 +5433,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>581964</v>
+        <v>581521</v>
       </c>
       <c r="R44" t="n">
-        <v>7193918</v>
+        <v>7194394</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5477,7 +5468,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5487,7 +5478,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5514,10 +5505,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120922538</v>
+        <v>120922566</v>
       </c>
       <c r="B45" t="n">
-        <v>79717</v>
+        <v>78601</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5526,20 +5517,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5554,10 +5545,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>581578</v>
+        <v>581743</v>
       </c>
       <c r="R45" t="n">
-        <v>7194309</v>
+        <v>7194127</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5589,7 +5580,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5599,7 +5590,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5626,7 +5617,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120922540</v>
+        <v>120922562</v>
       </c>
       <c r="B46" t="n">
         <v>78601</v>
@@ -5666,10 +5657,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>581580</v>
+        <v>581708</v>
       </c>
       <c r="R46" t="n">
-        <v>7194313</v>
+        <v>7194148</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5701,7 +5692,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5711,7 +5702,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5738,10 +5729,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120922578</v>
+        <v>120922569</v>
       </c>
       <c r="B47" t="n">
-        <v>82385</v>
+        <v>90697</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5754,21 +5745,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5778,10 +5769,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581966</v>
+        <v>581871</v>
       </c>
       <c r="R47" t="n">
-        <v>7193919</v>
+        <v>7194030</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5813,7 +5804,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5823,7 +5814,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5850,10 +5841,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120922541</v>
+        <v>120922544</v>
       </c>
       <c r="B48" t="n">
-        <v>74706</v>
+        <v>79718</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5862,25 +5853,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6486</v>
+        <v>6464</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5893,7 +5884,7 @@
         <v>581586</v>
       </c>
       <c r="R48" t="n">
-        <v>7194270</v>
+        <v>7194249</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5925,7 +5916,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5935,7 +5926,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5962,10 +5953,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120922579</v>
+        <v>120922531</v>
       </c>
       <c r="B49" t="n">
-        <v>78601</v>
+        <v>90662</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5974,25 +5965,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6002,10 +5993,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581970</v>
+        <v>581540</v>
       </c>
       <c r="R49" t="n">
-        <v>7193921</v>
+        <v>7194351</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6037,7 +6028,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6047,7 +6038,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6074,10 +6065,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120922517</v>
+        <v>120922495</v>
       </c>
       <c r="B50" t="n">
-        <v>79718</v>
+        <v>57367</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6086,38 +6077,43 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6464</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581464</v>
+        <v>581553</v>
       </c>
       <c r="R50" t="n">
-        <v>7194676</v>
+        <v>7194369</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6149,7 +6145,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6159,7 +6155,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6186,10 +6182,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120922570</v>
+        <v>120922494</v>
       </c>
       <c r="B51" t="n">
-        <v>78601</v>
+        <v>57504</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6202,34 +6198,38 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581870</v>
+        <v>581567</v>
       </c>
       <c r="R51" t="n">
-        <v>7194030</v>
+        <v>7194353</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6298,10 +6298,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120922560</v>
+        <v>120922557</v>
       </c>
       <c r="B52" t="n">
-        <v>78601</v>
+        <v>97035</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6310,25 +6310,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6338,10 +6338,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581688</v>
+        <v>581627</v>
       </c>
       <c r="R52" t="n">
-        <v>7194164</v>
+        <v>7194202</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6410,10 +6410,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120922535</v>
+        <v>120922577</v>
       </c>
       <c r="B53" t="n">
-        <v>79711</v>
+        <v>90697</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6422,25 +6422,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>581563</v>
+        <v>581965</v>
       </c>
       <c r="R53" t="n">
-        <v>7194343</v>
+        <v>7193917</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6485,7 +6485,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6522,10 +6522,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120922575</v>
+        <v>120922519</v>
       </c>
       <c r="B54" t="n">
-        <v>78601</v>
+        <v>79683</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6538,21 +6538,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6562,10 +6562,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>581896</v>
+        <v>581392</v>
       </c>
       <c r="R54" t="n">
-        <v>7193954</v>
+        <v>7194541</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6634,10 +6634,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120922572</v>
+        <v>120922541</v>
       </c>
       <c r="B55" t="n">
-        <v>78601</v>
+        <v>74706</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6646,25 +6646,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6674,10 +6674,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>581899</v>
+        <v>581586</v>
       </c>
       <c r="R55" t="n">
-        <v>7193983</v>
+        <v>7194270</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -6709,7 +6709,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6746,10 +6746,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120922534</v>
+        <v>120922542</v>
       </c>
       <c r="B56" t="n">
-        <v>79683</v>
+        <v>78601</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6762,21 +6762,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6786,10 +6786,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>581561</v>
+        <v>581583</v>
       </c>
       <c r="R56" t="n">
-        <v>7194344</v>
+        <v>7194274</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6821,7 +6821,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6858,7 +6858,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120922530</v>
+        <v>120922491</v>
       </c>
       <c r="B57" t="n">
         <v>78601</v>
@@ -6898,10 +6898,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>581521</v>
+        <v>581713</v>
       </c>
       <c r="R57" t="n">
-        <v>7194394</v>
+        <v>7194249</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6970,10 +6970,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120922565</v>
+        <v>120922533</v>
       </c>
       <c r="B58" t="n">
-        <v>82385</v>
+        <v>79682</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6986,21 +6986,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7010,10 +7010,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>581743</v>
+        <v>581561</v>
       </c>
       <c r="R58" t="n">
-        <v>7194126</v>
+        <v>7194344</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7045,7 +7045,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7082,10 +7082,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120922492</v>
+        <v>120922573</v>
       </c>
       <c r="B59" t="n">
-        <v>91052</v>
+        <v>90697</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7094,25 +7094,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7122,10 +7122,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>581638</v>
+        <v>581899</v>
       </c>
       <c r="R59" t="n">
-        <v>7194287</v>
+        <v>7193981</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7157,7 +7157,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7194,10 +7194,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120922519</v>
+        <v>120922526</v>
       </c>
       <c r="B60" t="n">
-        <v>79683</v>
+        <v>90693</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7210,21 +7210,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2081</v>
+        <v>1108</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7234,10 +7234,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>581392</v>
+        <v>581485</v>
       </c>
       <c r="R60" t="n">
-        <v>7194541</v>
+        <v>7194429</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7269,7 +7269,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7279,7 +7279,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7306,10 +7306,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120922566</v>
+        <v>120922517</v>
       </c>
       <c r="B61" t="n">
-        <v>78601</v>
+        <v>79718</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7318,25 +7318,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7346,10 +7346,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>581743</v>
+        <v>581464</v>
       </c>
       <c r="R61" t="n">
-        <v>7194127</v>
+        <v>7194676</v>
       </c>
       <c r="S61" t="n">
         <v>25</v>
@@ -7381,7 +7381,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7418,10 +7418,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120922557</v>
+        <v>120922550</v>
       </c>
       <c r="B62" t="n">
-        <v>97035</v>
+        <v>79718</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7434,21 +7434,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7458,10 +7458,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>581627</v>
+        <v>581585</v>
       </c>
       <c r="R62" t="n">
-        <v>7194202</v>
+        <v>7194233</v>
       </c>
       <c r="S62" t="n">
         <v>25</v>
@@ -7493,7 +7493,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7530,7 +7530,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120922571</v>
+        <v>120922564</v>
       </c>
       <c r="B63" t="n">
         <v>78601</v>
@@ -7570,10 +7570,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>581891</v>
+        <v>581774</v>
       </c>
       <c r="R63" t="n">
-        <v>7193993</v>
+        <v>7194115</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -7605,7 +7605,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7642,10 +7642,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120922521</v>
+        <v>120922496</v>
       </c>
       <c r="B64" t="n">
-        <v>79683</v>
+        <v>78601</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7658,21 +7658,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7682,10 +7682,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>581397</v>
+        <v>581553</v>
       </c>
       <c r="R64" t="n">
-        <v>7194475</v>
+        <v>7194365</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -7717,7 +7717,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7754,10 +7754,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120922563</v>
+        <v>120922529</v>
       </c>
       <c r="B65" t="n">
-        <v>90693</v>
+        <v>74708</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7770,21 +7770,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1108</v>
+        <v>6440</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7794,10 +7794,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>581730</v>
+        <v>581524</v>
       </c>
       <c r="R65" t="n">
-        <v>7194140</v>
+        <v>7194389</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7866,7 +7866,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120922548</v>
+        <v>120922539</v>
       </c>
       <c r="B66" t="n">
         <v>79718</v>
@@ -7906,10 +7906,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>581602</v>
+        <v>581579</v>
       </c>
       <c r="R66" t="n">
-        <v>7194242</v>
+        <v>7194310</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -7941,7 +7941,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7978,10 +7978,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120922516</v>
+        <v>120922552</v>
       </c>
       <c r="B67" t="n">
-        <v>78601</v>
+        <v>94496</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7990,25 +7990,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>2813</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8018,10 +8018,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>581511</v>
+        <v>581589</v>
       </c>
       <c r="R67" t="n">
-        <v>7194758</v>
+        <v>7194225</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8053,7 +8053,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8063,7 +8063,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8090,10 +8090,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120922581</v>
+        <v>120922538</v>
       </c>
       <c r="B68" t="n">
-        <v>78601</v>
+        <v>79717</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8102,20 +8102,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8130,10 +8130,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>581973</v>
+        <v>581578</v>
       </c>
       <c r="R68" t="n">
-        <v>7193915</v>
+        <v>7194309</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8202,10 +8202,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120922580</v>
+        <v>120922581</v>
       </c>
       <c r="B69" t="n">
-        <v>82385</v>
+        <v>78601</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8218,21 +8218,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8242,10 +8242,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>581971</v>
+        <v>581973</v>
       </c>
       <c r="R69" t="n">
-        <v>7193909</v>
+        <v>7193915</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8314,10 +8314,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120922490</v>
+        <v>120922568</v>
       </c>
       <c r="B70" t="n">
-        <v>78601</v>
+        <v>91137</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8326,25 +8326,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8354,10 +8354,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>581727</v>
+        <v>581867</v>
       </c>
       <c r="R70" t="n">
-        <v>7194249</v>
+        <v>7194029</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8389,7 +8389,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8426,7 +8426,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120922542</v>
+        <v>120922498</v>
       </c>
       <c r="B71" t="n">
         <v>78601</v>
@@ -8466,10 +8466,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>581583</v>
+        <v>581663</v>
       </c>
       <c r="R71" t="n">
-        <v>7194274</v>
+        <v>7194338</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8501,7 +8501,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8538,7 +8538,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120922583</v>
+        <v>120922575</v>
       </c>
       <c r="B72" t="n">
         <v>78601</v>
@@ -8578,10 +8578,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>581974</v>
+        <v>581896</v>
       </c>
       <c r="R72" t="n">
-        <v>7193913</v>
+        <v>7193954</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -8613,7 +8613,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8650,10 +8650,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120922536</v>
+        <v>120922556</v>
       </c>
       <c r="B73" t="n">
-        <v>79718</v>
+        <v>78690</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8666,21 +8666,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6464</v>
+        <v>6450</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8690,10 +8690,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>581563</v>
+        <v>581593</v>
       </c>
       <c r="R73" t="n">
-        <v>7194343</v>
+        <v>7194223</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8762,10 +8762,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120922533</v>
+        <v>120922567</v>
       </c>
       <c r="B74" t="n">
-        <v>79682</v>
+        <v>78601</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8778,21 +8778,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8802,10 +8802,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>581561</v>
+        <v>581802</v>
       </c>
       <c r="R74" t="n">
-        <v>7194344</v>
+        <v>7194113</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -8837,7 +8837,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8874,10 +8874,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120922499</v>
+        <v>120922580</v>
       </c>
       <c r="B75" t="n">
-        <v>78601</v>
+        <v>82385</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8890,21 +8890,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8914,10 +8914,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>581705</v>
+        <v>581971</v>
       </c>
       <c r="R75" t="n">
-        <v>7194365</v>
+        <v>7193909</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -8949,7 +8949,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:49</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8986,10 +8986,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120922568</v>
+        <v>120922534</v>
       </c>
       <c r="B76" t="n">
-        <v>91137</v>
+        <v>79683</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8998,25 +8998,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1209</v>
+        <v>2081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9026,10 +9026,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>581867</v>
+        <v>581561</v>
       </c>
       <c r="R76" t="n">
-        <v>7194029</v>
+        <v>7194344</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9061,7 +9061,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9098,10 +9098,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120922496</v>
+        <v>120922518</v>
       </c>
       <c r="B77" t="n">
-        <v>78601</v>
+        <v>79683</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9114,21 +9114,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9138,10 +9138,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>581553</v>
+        <v>581464</v>
       </c>
       <c r="R77" t="n">
-        <v>7194365</v>
+        <v>7194676</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -9173,7 +9173,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9210,10 +9210,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120922556</v>
+        <v>120922523</v>
       </c>
       <c r="B78" t="n">
-        <v>78690</v>
+        <v>79718</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9226,21 +9226,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6450</v>
+        <v>6464</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9250,10 +9250,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>581593</v>
+        <v>581415</v>
       </c>
       <c r="R78" t="n">
-        <v>7194223</v>
+        <v>7194476</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -9285,7 +9285,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9322,10 +9322,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120922529</v>
+        <v>120922493</v>
       </c>
       <c r="B79" t="n">
-        <v>74708</v>
+        <v>78601</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9338,21 +9338,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9362,10 +9362,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>581524</v>
+        <v>581641</v>
       </c>
       <c r="R79" t="n">
-        <v>7194389</v>
+        <v>7194292</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -9397,7 +9397,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD79" t="b">

--- a/artfynd/A 42063-2024 artfynd.xlsx
+++ b/artfynd/A 42063-2024 artfynd.xlsx
@@ -2247,10 +2247,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120922565</v>
+        <v>120922490</v>
       </c>
       <c r="B16" t="n">
-        <v>82385</v>
+        <v>78601</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2263,21 +2263,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>581743</v>
+        <v>581727</v>
       </c>
       <c r="R16" t="n">
-        <v>7194126</v>
+        <v>7194249</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2359,10 +2359,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120922576</v>
+        <v>120922536</v>
       </c>
       <c r="B17" t="n">
-        <v>90983</v>
+        <v>79718</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2371,25 +2371,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2399,10 +2399,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581964</v>
+        <v>581563</v>
       </c>
       <c r="R17" t="n">
-        <v>7193918</v>
+        <v>7194343</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:48</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2471,10 +2471,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120922492</v>
+        <v>120922565</v>
       </c>
       <c r="B18" t="n">
-        <v>91052</v>
+        <v>82385</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2483,25 +2483,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1506</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581638</v>
+        <v>581743</v>
       </c>
       <c r="R18" t="n">
-        <v>7194287</v>
+        <v>7194126</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2546,7 +2546,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2583,10 +2583,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120922563</v>
+        <v>120922576</v>
       </c>
       <c r="B19" t="n">
-        <v>90693</v>
+        <v>90983</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2599,21 +2599,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581730</v>
+        <v>581964</v>
       </c>
       <c r="R19" t="n">
-        <v>7194140</v>
+        <v>7193918</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2658,7 +2658,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2695,10 +2695,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120922490</v>
+        <v>120922492</v>
       </c>
       <c r="B20" t="n">
-        <v>78601</v>
+        <v>91052</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2707,25 +2707,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1506</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2735,10 +2735,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581727</v>
+        <v>581638</v>
       </c>
       <c r="R20" t="n">
-        <v>7194249</v>
+        <v>7194287</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2807,10 +2807,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120922536</v>
+        <v>120922563</v>
       </c>
       <c r="B21" t="n">
-        <v>79718</v>
+        <v>90693</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2819,25 +2819,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6464</v>
+        <v>1108</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2847,10 +2847,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581563</v>
+        <v>581730</v>
       </c>
       <c r="R21" t="n">
-        <v>7194343</v>
+        <v>7194140</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -5729,10 +5729,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120922569</v>
+        <v>120922495</v>
       </c>
       <c r="B47" t="n">
-        <v>90697</v>
+        <v>57367</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5745,34 +5745,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>581871</v>
+        <v>581553</v>
       </c>
       <c r="R47" t="n">
-        <v>7194030</v>
+        <v>7194369</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5804,7 +5809,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5814,7 +5819,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5841,10 +5846,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120922544</v>
+        <v>120922494</v>
       </c>
       <c r="B48" t="n">
-        <v>79718</v>
+        <v>57504</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5853,38 +5858,42 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>581586</v>
+        <v>581567</v>
       </c>
       <c r="R48" t="n">
-        <v>7194249</v>
+        <v>7194353</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5916,7 +5925,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5926,7 +5935,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5953,10 +5962,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120922531</v>
+        <v>120922557</v>
       </c>
       <c r="B49" t="n">
-        <v>90662</v>
+        <v>97035</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5969,21 +5978,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5993,10 +6002,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>581540</v>
+        <v>581627</v>
       </c>
       <c r="R49" t="n">
-        <v>7194351</v>
+        <v>7194202</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6028,7 +6037,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6038,7 +6047,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6065,10 +6074,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120922495</v>
+        <v>120922569</v>
       </c>
       <c r="B50" t="n">
-        <v>57367</v>
+        <v>90697</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6081,39 +6090,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>581553</v>
+        <v>581871</v>
       </c>
       <c r="R50" t="n">
-        <v>7194369</v>
+        <v>7194030</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6145,7 +6149,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6155,7 +6159,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6182,10 +6186,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120922494</v>
+        <v>120922544</v>
       </c>
       <c r="B51" t="n">
-        <v>57504</v>
+        <v>79718</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6194,42 +6198,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Luspberget, Vojmsjödammen, Ås lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>581567</v>
+        <v>581586</v>
       </c>
       <c r="R51" t="n">
-        <v>7194353</v>
+        <v>7194249</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6261,7 +6261,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6298,10 +6298,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120922557</v>
+        <v>120922531</v>
       </c>
       <c r="B52" t="n">
-        <v>97035</v>
+        <v>90662</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6314,21 +6314,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6338,10 +6338,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>581627</v>
+        <v>581540</v>
       </c>
       <c r="R52" t="n">
-        <v>7194202</v>
+        <v>7194351</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 42063-2024 artfynd.xlsx
+++ b/artfynd/A 42063-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120922516</v>
+        <v>120922518</v>
       </c>
       <c r="B2" t="n">
-        <v>78601</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581511</v>
+        <v>581464</v>
       </c>
       <c r="R2" t="n">
-        <v>7194758</v>
+        <v>7194676</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,37 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120922517</v>
+        <v>120922516</v>
       </c>
       <c r="B3" t="n">
-        <v>79718</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581464</v>
+        <v>581511</v>
       </c>
       <c r="R3" t="n">
-        <v>7194676</v>
+        <v>7194758</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120922518</v>
+        <v>120922517</v>
       </c>
       <c r="B4" t="n">
-        <v>79683</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
